--- a/AAII_Financials/Yearly/PL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PL_YR_FIN.xlsx
@@ -876,13 +876,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>167600</v>
+        <v>6200</v>
       </c>
       <c r="E14" s="3">
-        <v>29800</v>
+        <v>14700</v>
       </c>
       <c r="F14" s="3">
-        <v>-5500</v>
+        <v>8200</v>
       </c>
       <c r="G14" s="3">
         <v>-6600</v>
@@ -1021,13 +1021,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2100</v>
+        <v>163500</v>
       </c>
       <c r="E20" s="3">
-        <v>-2400</v>
+        <v>12700</v>
       </c>
       <c r="F20" s="3">
-        <v>-900</v>
+        <v>-14600</v>
       </c>
       <c r="G20" s="3">
         <v>-300</v>
@@ -1051,13 +1051,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-47100</v>
+        <v>-208500</v>
       </c>
       <c r="E21" s="3">
-        <v>-57200</v>
+        <v>-72300</v>
       </c>
       <c r="F21" s="3">
-        <v>-114900</v>
+        <v>-101200</v>
       </c>
       <c r="G21" s="3">
         <v>-134400</v>
@@ -1381,13 +1381,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2100</v>
+        <v>-163500</v>
       </c>
       <c r="E32" s="3">
-        <v>2400</v>
+        <v>-12700</v>
       </c>
       <c r="F32" s="3">
-        <v>900</v>
+        <v>14600</v>
       </c>
       <c r="G32" s="3">
         <v>300</v>
